--- a/Estimate_Template.xlsx
+++ b/Estimate_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smrazik\Desktop\Estimates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0561E0C-C65B-469B-992B-F269895CC7BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513137F4-D2EB-4DE4-A28C-7B5BC71B5D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="38" r:id="rId1"/>
@@ -70,6 +70,28 @@
     </comment>
   </commentList>
 </comments>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4701,46 +4723,141 @@
     <xf numFmtId="169" fontId="28" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4750,12 +4867,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
@@ -4797,70 +4908,31 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4868,50 +4940,6 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -4927,12 +4955,6 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -6345,101 +6367,101 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="9"/>
-      <c r="B1" s="170" t="s">
+      <c r="B1" s="162" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="10"/>
-      <c r="H1" s="170" t="s">
+      <c r="H1" s="162" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="172"/>
-      <c r="J1" s="172"/>
-      <c r="K1" s="172"/>
-      <c r="L1" s="172"/>
-      <c r="M1" s="172"/>
-      <c r="N1" s="172"/>
+      <c r="I1" s="164"/>
+      <c r="J1" s="164"/>
+      <c r="K1" s="164"/>
+      <c r="L1" s="164"/>
+      <c r="M1" s="164"/>
+      <c r="N1" s="164"/>
     </row>
     <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9"/>
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="165" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="138"/>
-      <c r="D2" s="138"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="166"/>
+      <c r="E2" s="166"/>
+      <c r="F2" s="166"/>
       <c r="G2" s="12"/>
-      <c r="H2" s="173" t="s">
+      <c r="H2" s="165" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="171"/>
-      <c r="J2" s="171"/>
-      <c r="K2" s="171"/>
-      <c r="L2" s="171"/>
-      <c r="M2" s="171"/>
-      <c r="N2" s="171"/>
+      <c r="I2" s="163"/>
+      <c r="J2" s="163"/>
+      <c r="K2" s="163"/>
+      <c r="L2" s="163"/>
+      <c r="M2" s="163"/>
+      <c r="N2" s="163"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9"/>
-      <c r="B3" s="174" t="str">
+      <c r="B3" s="167" t="str">
         <f>"COST FOR "&amp; UPPER(Sheet1!B1)</f>
         <v xml:space="preserve">COST FOR </v>
       </c>
-      <c r="C3" s="138"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="138"/>
-      <c r="F3" s="138"/>
+      <c r="C3" s="166"/>
+      <c r="D3" s="166"/>
+      <c r="E3" s="166"/>
+      <c r="F3" s="166"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="175" t="s">
+      <c r="H3" s="168" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="176"/>
-      <c r="J3" s="176"/>
-      <c r="K3" s="176"/>
-      <c r="L3" s="176"/>
-      <c r="M3" s="176"/>
-      <c r="N3" s="176"/>
+      <c r="I3" s="169"/>
+      <c r="J3" s="169"/>
+      <c r="K3" s="169"/>
+      <c r="L3" s="169"/>
+      <c r="M3" s="169"/>
+      <c r="N3" s="169"/>
     </row>
     <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9"/>
       <c r="B4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="161" t="e">
+      <c r="C4" s="170" t="e">
         <f>LEFT(Sheet1!B5, LEN(Sheet1!B5)-9)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D4" s="162"/>
-      <c r="E4" s="162"/>
-      <c r="F4" s="162"/>
-      <c r="G4" s="163" t="str">
+      <c r="D4" s="171"/>
+      <c r="E4" s="171"/>
+      <c r="F4" s="171"/>
+      <c r="G4" s="172" t="str">
         <f>"COST FOR "&amp; UPPER(Sheet1!B1)</f>
         <v xml:space="preserve">COST FOR </v>
       </c>
-      <c r="H4" s="164"/>
-      <c r="I4" s="164"/>
-      <c r="J4" s="164"/>
-      <c r="K4" s="164"/>
-      <c r="L4" s="164"/>
-      <c r="M4" s="165"/>
-      <c r="N4" s="138"/>
+      <c r="H4" s="173"/>
+      <c r="I4" s="173"/>
+      <c r="J4" s="173"/>
+      <c r="K4" s="173"/>
+      <c r="L4" s="173"/>
+      <c r="M4" s="174"/>
+      <c r="N4" s="166"/>
     </row>
     <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="133">
+      <c r="C5" s="150">
         <f>Sheet1!B7</f>
         <v>0</v>
       </c>
-      <c r="D5" s="166"/>
-      <c r="E5" s="166"/>
-      <c r="F5" s="166"/>
+      <c r="D5" s="153"/>
+      <c r="E5" s="153"/>
+      <c r="F5" s="153"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -6454,44 +6476,44 @@
       <c r="B6" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="133" t="str">
+      <c r="C6" s="150" t="str">
         <f>Sheet1!B10&amp;"' X "&amp;Sheet1!B11&amp;"' X "&amp;Sheet1!B12&amp;""""</f>
         <v>' X ' X "</v>
       </c>
-      <c r="D6" s="166"/>
-      <c r="E6" s="166"/>
-      <c r="F6" s="166"/>
+      <c r="D6" s="153"/>
+      <c r="E6" s="153"/>
+      <c r="F6" s="153"/>
       <c r="G6" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="H6" s="167">
+      <c r="H6" s="175">
         <f>Sheet1!B3</f>
         <v>0</v>
       </c>
-      <c r="I6" s="162"/>
-      <c r="J6" s="168" t="s">
+      <c r="I6" s="171"/>
+      <c r="J6" s="176" t="s">
         <v>0</v>
       </c>
-      <c r="K6" s="138"/>
-      <c r="L6" s="138"/>
-      <c r="M6" s="161" t="e">
+      <c r="K6" s="166"/>
+      <c r="L6" s="166"/>
+      <c r="M6" s="170" t="e">
         <f>C4</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N6" s="169"/>
+      <c r="N6" s="177"/>
     </row>
     <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
       <c r="B7" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="133">
+      <c r="C7" s="150">
         <f>Sheet1!B1</f>
         <v>0</v>
       </c>
-      <c r="D7" s="166"/>
-      <c r="E7" s="166"/>
-      <c r="F7" s="166"/>
+      <c r="D7" s="153"/>
+      <c r="E7" s="153"/>
+      <c r="F7" s="153"/>
       <c r="G7" s="15"/>
       <c r="H7" s="17"/>
       <c r="I7" s="17"/>
@@ -6506,13 +6528,13 @@
       <c r="B8" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="177">
+      <c r="C8" s="154">
         <f>Sheet1!B9</f>
         <v>0</v>
       </c>
-      <c r="D8" s="178"/>
-      <c r="E8" s="178"/>
-      <c r="F8" s="178"/>
+      <c r="D8" s="155"/>
+      <c r="E8" s="155"/>
+      <c r="F8" s="155"/>
       <c r="G8" s="20" t="s">
         <v>22</v>
       </c>
@@ -6528,10 +6550,10 @@
       <c r="N8" s="22"/>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="137" t="s">
+      <c r="A9" s="191" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="138"/>
+      <c r="B9" s="166"/>
       <c r="C9" s="19"/>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
@@ -6556,10 +6578,10 @@
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="139" t="s">
+      <c r="A10" s="192" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="140"/>
+      <c r="B10" s="193"/>
       <c r="C10" s="28" t="s">
         <v>36</v>
       </c>
@@ -6608,7 +6630,7 @@
         <f>A11*C11*E11</f>
         <v>0</v>
       </c>
-      <c r="G11" s="179" t="s">
+      <c r="G11" s="156" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="25" t="s">
@@ -6645,7 +6667,7 @@
         <f>A12*C12*E12</f>
         <v>0</v>
       </c>
-      <c r="G12" s="180"/>
+      <c r="G12" s="157"/>
       <c r="H12" s="25">
         <f>C8</f>
         <v>0</v>
@@ -6658,10 +6680,10 @@
       <c r="N12" s="25"/>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="139" t="s">
+      <c r="A13" s="192" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="140"/>
+      <c r="B13" s="193"/>
       <c r="C13" s="28" t="s">
         <v>36</v>
       </c>
@@ -6754,10 +6776,10 @@
     <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="30"/>
       <c r="B16" s="30"/>
-      <c r="C16" s="181" t="s">
+      <c r="C16" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="182"/>
+      <c r="D16" s="161"/>
       <c r="E16" s="44">
         <f>Sheet1!B13</f>
         <v>0</v>
@@ -6781,10 +6803,10 @@
       <c r="N16" s="9"/>
     </row>
     <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="141" t="s">
+      <c r="A17" s="194" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="142"/>
+      <c r="B17" s="195"/>
       <c r="C17" s="46">
         <f>(SUM(A11*C11)+(A12*C12)+(A14*C14)+(A15*C15))*K16</f>
         <v>0</v>
@@ -6809,10 +6831,10 @@
       <c r="N17" s="9"/>
     </row>
     <row r="18" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="143" t="s">
+      <c r="A18" s="196" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="140"/>
+      <c r="B18" s="193"/>
       <c r="C18" s="49" t="s">
         <v>56</v>
       </c>
@@ -6828,19 +6850,19 @@
       <c r="J18" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="K18" s="53" t="e">
+      <c r="K18" s="53">
         <f>F47</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
       <c r="N18" s="9"/>
     </row>
     <row r="19" spans="1:16" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="133" t="s">
+      <c r="A19" s="150" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="133"/>
+      <c r="B19" s="150"/>
       <c r="C19" s="79"/>
       <c r="D19" s="58"/>
       <c r="E19" s="58"/>
@@ -6857,10 +6879,10 @@
       <c r="P19" s="4"/>
     </row>
     <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="139" t="s">
+      <c r="A20" s="192" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="146"/>
+      <c r="B20" s="198"/>
       <c r="C20" s="28" t="s">
         <v>36</v>
       </c>
@@ -6875,13 +6897,13 @@
       </c>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="134" t="s">
+      <c r="I20" s="158" t="s">
         <v>25</v>
       </c>
-      <c r="J20" s="145"/>
+      <c r="J20" s="159"/>
       <c r="K20" s="56" t="e">
         <f>K18*(Sheet1!#REF!/100)</f>
-        <v>#N/A</v>
+        <v>#REF!</v>
       </c>
       <c r="L20" s="9"/>
       <c r="M20" s="9"/>
@@ -6950,13 +6972,13 @@
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="134" t="s">
+      <c r="I22" s="158" t="s">
         <v>26</v>
       </c>
-      <c r="J22" s="145"/>
+      <c r="J22" s="159"/>
       <c r="K22" s="56" t="e">
         <f>K18*(Sheet1!#REF!/100)</f>
-        <v>#N/A</v>
+        <v>#REF!</v>
       </c>
       <c r="L22" s="58"/>
       <c r="M22" s="58"/>
@@ -7021,16 +7043,16 @@
       </c>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="134" t="s">
+      <c r="I24" s="158" t="s">
         <v>27</v>
       </c>
-      <c r="J24" s="145"/>
+      <c r="J24" s="159"/>
       <c r="K24" s="60"/>
       <c r="L24" s="58"/>
-      <c r="M24" s="144" t="s">
+      <c r="M24" s="197" t="s">
         <v>63</v>
       </c>
-      <c r="N24" s="138"/>
+      <c r="N24" s="166"/>
     </row>
     <row r="25" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="30">
@@ -7090,11 +7112,11 @@
         <v>#N/A</v>
       </c>
       <c r="G26" s="9"/>
-      <c r="H26" s="183" t="s">
+      <c r="H26" s="199" t="s">
         <v>60</v>
       </c>
-      <c r="I26" s="184"/>
-      <c r="J26" s="184"/>
+      <c r="I26" s="200"/>
+      <c r="J26" s="200"/>
       <c r="K26" s="59" t="s">
         <v>61</v>
       </c>
@@ -7300,14 +7322,14 @@
         <v>#N/A</v>
       </c>
       <c r="G32" s="9"/>
-      <c r="H32" s="134" t="s">
+      <c r="H32" s="158" t="s">
         <v>13</v>
       </c>
-      <c r="I32" s="135"/>
-      <c r="J32" s="136"/>
-      <c r="K32" s="136"/>
-      <c r="L32" s="136"/>
-      <c r="M32" s="136"/>
+      <c r="I32" s="190"/>
+      <c r="J32" s="138"/>
+      <c r="K32" s="138"/>
+      <c r="L32" s="138"/>
+      <c r="M32" s="138"/>
       <c r="N32" s="22"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7337,12 +7359,12 @@
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
-      <c r="J33" s="149" t="s">
+      <c r="J33" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="K33" s="149"/>
-      <c r="L33" s="150"/>
-      <c r="M33" s="150"/>
+      <c r="K33" s="135"/>
+      <c r="L33" s="136"/>
+      <c r="M33" s="136"/>
       <c r="N33" s="58" t="s">
         <v>8</v>
       </c>
@@ -7372,14 +7394,14 @@
         <v>#N/A</v>
       </c>
       <c r="G34" s="9"/>
-      <c r="H34" s="185" t="s">
+      <c r="H34" s="137" t="s">
         <v>9</v>
       </c>
-      <c r="I34" s="149"/>
-      <c r="J34" s="136"/>
-      <c r="K34" s="136"/>
-      <c r="L34" s="136"/>
-      <c r="M34" s="136"/>
+      <c r="I34" s="135"/>
+      <c r="J34" s="138"/>
+      <c r="K34" s="138"/>
+      <c r="L34" s="138"/>
+      <c r="M34" s="138"/>
       <c r="N34" s="22"/>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7409,12 +7431,12 @@
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
-      <c r="J35" s="149" t="s">
+      <c r="J35" s="135" t="s">
         <v>19</v>
       </c>
-      <c r="K35" s="149"/>
-      <c r="L35" s="150"/>
-      <c r="M35" s="150"/>
+      <c r="K35" s="135"/>
+      <c r="L35" s="136"/>
+      <c r="M35" s="136"/>
       <c r="N35" s="58" t="s">
         <v>8</v>
       </c>
@@ -7469,79 +7491,79 @@
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="G37" s="151" t="s">
+      <c r="G37" s="180" t="s">
         <v>10</v>
       </c>
-      <c r="H37" s="152"/>
+      <c r="H37" s="181"/>
       <c r="I37" s="3"/>
-      <c r="J37" s="151" t="s">
+      <c r="J37" s="180" t="s">
         <v>11</v>
       </c>
-      <c r="K37" s="153"/>
+      <c r="K37" s="182"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
     </row>
     <row r="38" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="195" t="s">
+      <c r="A38" s="148" t="s">
         <v>100</v>
       </c>
-      <c r="B38" s="196"/>
-      <c r="C38" s="196"/>
-      <c r="D38" s="196"/>
-      <c r="E38" s="196"/>
-      <c r="F38" s="51" t="e">
-        <f>SUM(F21:F37)</f>
-        <v>#N/A</v>
+      <c r="B38" s="149"/>
+      <c r="C38" s="149"/>
+      <c r="D38" s="149"/>
+      <c r="E38" s="149"/>
+      <c r="F38" s="51" cm="1">
+        <f t="array" ref="F38">SUM(IFERROR(F21:F37,0))</f>
+        <v>0</v>
       </c>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
-      <c r="L38" s="154" t="s">
+      <c r="L38" s="183" t="s">
         <v>20</v>
       </c>
-      <c r="M38" s="152"/>
+      <c r="M38" s="181"/>
       <c r="N38" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="192" t="s">
+      <c r="A39" s="145" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="193"/>
-      <c r="C39" s="193"/>
-      <c r="D39" s="194"/>
+      <c r="B39" s="146"/>
+      <c r="C39" s="146"/>
+      <c r="D39" s="147"/>
       <c r="E39" s="82">
         <v>1</v>
       </c>
-      <c r="F39" s="51" t="e">
+      <c r="F39" s="51">
         <f>F38*K16</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="133" t="s">
+      <c r="A40" s="150" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="133"/>
+      <c r="B40" s="150"/>
       <c r="C40" s="72"/>
       <c r="D40" s="83"/>
       <c r="E40" s="83"/>
       <c r="F40" s="83"/>
-      <c r="K40" s="155" t="s">
+      <c r="K40" s="184" t="s">
         <v>28</v>
       </c>
-      <c r="L40" s="156"/>
-      <c r="M40" s="157"/>
+      <c r="L40" s="185"/>
+      <c r="M40" s="186"/>
       <c r="N40" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="197" t="s">
+      <c r="A41" s="151" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="198"/>
+      <c r="B41" s="152"/>
       <c r="C41" s="28" t="s">
         <v>36</v>
       </c>
@@ -7555,16 +7577,16 @@
         <v>3</v>
       </c>
       <c r="I41" s="2"/>
-      <c r="K41" s="158"/>
-      <c r="L41" s="159"/>
-      <c r="M41" s="159"/>
-      <c r="N41" s="160"/>
+      <c r="K41" s="187"/>
+      <c r="L41" s="188"/>
+      <c r="M41" s="188"/>
+      <c r="N41" s="189"/>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="190" t="s">
+      <c r="A42" s="143" t="s">
         <v>101</v>
       </c>
-      <c r="B42" s="191"/>
+      <c r="B42" s="144"/>
       <c r="C42" s="33"/>
       <c r="D42" s="33" t="s">
         <v>50</v>
@@ -7576,20 +7598,20 @@
         <f>E42*C42</f>
         <v>0</v>
       </c>
-      <c r="K42" s="186" t="s">
+      <c r="K42" s="139" t="s">
         <v>14</v>
       </c>
-      <c r="L42" s="187"/>
-      <c r="M42" s="187"/>
+      <c r="L42" s="140"/>
+      <c r="M42" s="140"/>
       <c r="N42" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="190" t="s">
+      <c r="A43" s="143" t="s">
         <v>102</v>
       </c>
-      <c r="B43" s="191"/>
+      <c r="B43" s="144"/>
       <c r="C43" s="73"/>
       <c r="D43" s="33" t="s">
         <v>49</v>
@@ -7601,20 +7623,20 @@
         <f>E43*C43</f>
         <v>0</v>
       </c>
-      <c r="K43" s="147" t="s">
+      <c r="K43" s="178" t="s">
         <v>64</v>
       </c>
-      <c r="L43" s="148"/>
-      <c r="M43" s="148"/>
+      <c r="L43" s="179"/>
+      <c r="M43" s="179"/>
       <c r="N43" s="8" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="190" t="s">
+      <c r="A44" s="143" t="s">
         <v>103</v>
       </c>
-      <c r="B44" s="191"/>
+      <c r="B44" s="144"/>
       <c r="C44" s="73"/>
       <c r="D44" s="33" t="s">
         <v>104</v>
@@ -7626,10 +7648,10 @@
       </c>
     </row>
     <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="188" t="s">
+      <c r="A45" s="141" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="189"/>
+      <c r="B45" s="142"/>
       <c r="C45" s="49"/>
       <c r="D45" s="49"/>
       <c r="E45" s="50"/>
@@ -7654,9 +7676,9 @@
       <c r="C47" s="85"/>
       <c r="D47" s="85"/>
       <c r="E47" s="85"/>
-      <c r="F47" s="86" t="e">
+      <c r="F47" s="86">
         <f>F45+F39+F18</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
@@ -7666,10 +7688,10 @@
       <c r="D48" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="E48" s="204" t="s">
+      <c r="E48" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="F48" s="205"/>
+      <c r="F48" s="134"/>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B49" s="74"/>
@@ -7698,45 +7720,6 @@
     <filterColumn colId="12" showButton="0"/>
   </autoFilter>
   <mergeCells count="51">
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="K42:M42"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="H1:N1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="H2:N2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="G4:N4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="K43:M43"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="K40:M40"/>
-    <mergeCell ref="K41:N41"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="H32:I32"/>
     <mergeCell ref="J32:M32"/>
@@ -7749,6 +7732,45 @@
     <mergeCell ref="I24:J24"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="H26:J26"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="G4:N4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H1:N1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="H2:N2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="K42:M42"/>
+    <mergeCell ref="K43:M43"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="K41:N41"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0" header="0.2" footer="0.25"/>
@@ -7828,36 +7850,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="199" t="s">
+      <c r="A1" s="201" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="200"/>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
-      <c r="I1" s="200"/>
-      <c r="J1" s="201"/>
+      <c r="B1" s="202"/>
+      <c r="C1" s="202"/>
+      <c r="D1" s="202"/>
+      <c r="E1" s="202"/>
+      <c r="F1" s="202"/>
+      <c r="G1" s="202"/>
+      <c r="H1" s="202"/>
+      <c r="I1" s="202"/>
+      <c r="J1" s="203"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="202" t="s">
+      <c r="A2" s="204" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="200"/>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="203" t="s">
+      <c r="B2" s="202"/>
+      <c r="C2" s="202"/>
+      <c r="D2" s="202"/>
+      <c r="E2" s="203"/>
+      <c r="F2" s="205" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="200"/>
+      <c r="G2" s="202"/>
       <c r="H2" s="87"/>
-      <c r="I2" s="202" t="s">
+      <c r="I2" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="201"/>
+      <c r="J2" s="203"/>
     </row>
     <row r="3" spans="1:10" ht="105" x14ac:dyDescent="0.2">
       <c r="A3" s="88" t="s">
